--- a/artfynd/A 42614-2024 artfynd.xlsx
+++ b/artfynd/A 42614-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120442251</v>
+        <v>120442222</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogen norr gamla vägen s landsvägen, Eret, Dlr</t>
+          <t>Gamla bron över Gettjärnsbäcken, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570724</v>
+        <v>570801</v>
       </c>
       <c r="R2" t="n">
-        <v>6694187</v>
+        <v>6694257</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera ställen i skogen norr och söder om landsvägen</t>
+          <t>Ca 20 hängen på minst 3 äldre granar invid bron över Gettjärnsbäcken, gamla vägen, sö nuvarande landsvägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,6 +788,245 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109137831</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norra Eret, hagen, Eret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>570666</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6694105</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120442251</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogen norr gamla vägen s landsvägen, Eret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>570724</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6694187</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På flera ställen i skogen norr och söder om landsvägen</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42614-2024 artfynd.xlsx
+++ b/artfynd/A 42614-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442222</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109137831</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,8 +1042,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120442251</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>